--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1260-277-CM25</t>
+          <t>937232-1136-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,28 +1408,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>30398.55</v>
+        <v>92320.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>937232-1136-CM25</t>
+          <t>1260-276-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,26 +1473,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>92320.2</v>
+        <v>19852.06</v>
       </c>
     </row>
     <row r="18">
@@ -1616,7 +1616,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1260-276-CM25</t>
+          <t>1260-277-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>19852.06</v>
+        <v>30398.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2429-3087-CM25</t>
+          <t>628-440-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1697,48 +1697,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XERTICA CHILE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.223.453-8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>30476.52</v>
+        <v>94180.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>628-440-CM25</t>
+          <t>3712-1170-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1763,47 +1767,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>94180.9792</v>
+        <v>56773.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3712-1170-CM25</t>
+          <t>628-483-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1828,27 +1828,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>56773.89</v>
+        <v>21145.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>628-483-CM25</t>
+          <t>870-391-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1889,27 +1889,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21145.11</v>
+        <v>3078.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>870-391-CM25</t>
+          <t>1426099-232-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1950,27 +1950,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3078.29</v>
+        <v>9282</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1426099-232-CM25</t>
+          <t>2429-3087-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2006,32 +2006,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9282</v>
+        <v>30476.52</v>
       </c>
     </row>
     <row r="27">
@@ -2535,7 +2535,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2777-925-CM25</t>
+          <t>2674-1249-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2555,32 +2555,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>49673.46</v>
+        <v>3171.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2674-1249-CM25</t>
+          <t>605-503-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.006.000-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3171.77</v>
+        <v>16779</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>605-503-CM25</t>
+          <t>2777-925-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2677,22 +2677,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.006.000-5</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Consejo de Defensa del Estado</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>16779</v>
+        <v>49673.46</v>
       </c>
     </row>
     <row r="38">
@@ -2840,7 +2840,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3191-6161-CM25</t>
+          <t>1036569-232-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2865,27 +2865,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>Gobierno Regional de Ñuble</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2063.75</v>
+        <v>1304.43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>918434-545-CM25</t>
+          <t>1075952-49-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5503.32</v>
+        <v>800.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1075952-49-CM25</t>
+          <t>918434-545-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>61.980.680-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>800.87</v>
+        <v>5503.32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1036569-232-CM25</t>
+          <t>3191-6161-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3048,27 +3048,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1304.43</v>
+        <v>2063.75</v>
       </c>
     </row>
     <row r="44">
@@ -3328,7 +3328,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3201-450-CM25</t>
+          <t>858-808-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3348,32 +3348,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3538.23</v>
+        <v>75372.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>858-808-CM25</t>
+          <t>3201-450-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3409,32 +3409,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>75372.16</v>
+        <v>3538.23</v>
       </c>
     </row>
     <row r="50">
@@ -3511,7 +3511,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2698-338-CM25</t>
+          <t>2665-1239-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.150.101-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>Dirección de Educación Municipal</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>73669.92999999999</v>
+        <v>211.43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2665-1239-CM25</t>
+          <t>1614-270-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3592,32 +3592,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.150.101-9</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>Superintendencia de Electricidad y Combustibles</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3627,13 +3627,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>211.43</v>
+        <v>28560</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1614-270-CM25</t>
+          <t>2698-338-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3658,27 +3658,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Superintendencia de Electricidad y Combustibles</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>28560</v>
+        <v>73669.92999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4125,7 +4125,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2582-4240-CM25</t>
+          <t>1385462-330-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4140,22 +4140,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4165,32 +4165,28 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>72854.17999999999</v>
+        <v>22983.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3703-676-CM25</t>
+          <t>1068038-145-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4210,32 +4206,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>Pasos Fronterizos</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4245,13 +4241,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8899.5</v>
+        <v>3804.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057491-21303-CM25</t>
+          <t>1133261-210-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4271,32 +4267,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4306,13 +4302,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>99960</v>
+        <v>7518.42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1385462-330-CM25</t>
+          <t>1172445-2366-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4337,27 +4333,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4367,13 +4363,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>22983.66</v>
+        <v>48452.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1133261-210-CM25</t>
+          <t>1057491-21303-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4393,32 +4389,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4428,13 +4424,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7518.42</v>
+        <v>99960</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1068038-145-CM25</t>
+          <t>3703-676-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4454,32 +4450,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pasos Fronterizos</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4489,13 +4485,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3804.83</v>
+        <v>8899.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1172445-2366-CM25</t>
+          <t>318-199-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4510,7 +4506,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4520,17 +4516,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>70.816.800-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4550,67 +4546,6 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>48452.04</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>318-199-CM25</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>dic-2025</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>70.816.800-9</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="n">
         <v>9939.360000000001</v>
       </c>
     </row>
